--- a/Documents/Refined_proposal_ChatGPT.xlsx
+++ b/Documents/Refined_proposal_ChatGPT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Business\Agentic Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Business\Agentic Code\Requirements_Tool_Local_AI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C648A2-CB94-4EF3-9C39-2FA91533C2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C706D512-DA27-4AF2-A9CB-B43056D14A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D17E0A88-1C2D-4A27-9B15-EB45CA17BC10}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>DeepSeek-R1:7b for content review and Gemma3:4b for structuring</t>
   </si>
   <si>
-    <t>List of functions/systems comprising the product</t>
-  </si>
-  <si>
     <t>Generic description of each function</t>
   </si>
   <si>
@@ -274,6 +271,9 @@
   </si>
   <si>
     <t>Author to Produce Initial version. Following review, AI can update this.</t>
+  </si>
+  <si>
+    <t>Product Name, Product Description, List of functions/systems comprising the product ,Hardware platform/Cloud platform/Software platform it will be based on for webapp, Android app, BFF and Backend plus Github link to save online in addtion to local</t>
   </si>
 </sst>
 </file>
@@ -731,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -748,23 +748,23 @@
         <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -772,35 +772,35 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -808,35 +808,35 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -844,31 +844,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -876,31 +876,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3">
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -908,31 +908,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3">
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -940,31 +940,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3">
         <v>6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -972,31 +972,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3">
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -1004,31 +1004,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3">
         <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/Refined_proposal_ChatGPT.xlsx
+++ b/Documents/Refined_proposal_ChatGPT.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Business\Agentic Code\Requirements_Tool_Local_AI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C706D512-DA27-4AF2-A9CB-B43056D14A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4160EB37-4130-4891-A192-A475C420ED4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D17E0A88-1C2D-4A27-9B15-EB45CA17BC10}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D17E0A88-1C2D-4A27-9B15-EB45CA17BC10}"/>
   </bookViews>
   <sheets>
     <sheet name="updated_ai_engineering_pipeline" sheetId="1" r:id="rId1"/>
+    <sheet name="Traceability_sheet" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="267">
   <si>
     <t>Stage</t>
   </si>
@@ -72,9 +73,6 @@
     <t>DeepSeek-R1:7b for content review and Gemma3:4b for structuring</t>
   </si>
   <si>
-    <t>Generic description of each function</t>
-  </si>
-  <si>
     <t>External product/system linkages</t>
   </si>
   <si>
@@ -96,9 +94,6 @@
     <t>High-level state machines</t>
   </si>
   <si>
-    <t>Flowcharts of functions</t>
-  </si>
-  <si>
     <t>Container Diagram (C4 Methodology)</t>
   </si>
   <si>
@@ -274,13 +269,571 @@
   </si>
   <si>
     <t>Product Name, Product Description, List of functions/systems comprising the product ,Hardware platform/Cloud platform/Software platform it will be based on for webapp, Android app, BFF and Backend plus Github link to save online in addtion to local</t>
+  </si>
+  <si>
+    <t>Flowcharts of functions. This will show cross-functional impact.</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>PRD</t>
+  </si>
+  <si>
+    <t>D1.1</t>
+  </si>
+  <si>
+    <t>D1.2</t>
+  </si>
+  <si>
+    <t>D1.3</t>
+  </si>
+  <si>
+    <t>D1.4</t>
+  </si>
+  <si>
+    <t>Product name</t>
+  </si>
+  <si>
+    <t>Deliverables</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Manually Typed in Initially</t>
+  </si>
+  <si>
+    <t>Reason for LLM Review</t>
+  </si>
+  <si>
+    <t>LLM Review</t>
+  </si>
+  <si>
+    <t>Check if name is not a funny name and makes sense? If not making sense, confirm with user if not give output that seems ok</t>
+  </si>
+  <si>
+    <t>Product Description</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Reason for Requesting</t>
+  </si>
+  <si>
+    <t>D1.2.1</t>
+  </si>
+  <si>
+    <t>D1.2.2</t>
+  </si>
+  <si>
+    <t>D1.2.3</t>
+  </si>
+  <si>
+    <t>This requirement capture app (RCA) will only state that lets proceed with product description.</t>
+  </si>
+  <si>
+    <t>This requirement capture app (RCA) will mention that name is required to create a new folder with Product Name at the default location. Default location is configurable in pipeline settings tab, if not will default to C:/RCA/&lt;Product_Name&gt;</t>
+  </si>
+  <si>
+    <t>Statement only</t>
+  </si>
+  <si>
+    <t>Business Purpose of Product</t>
+  </si>
+  <si>
+    <t>Explain for a new user what will happen on first click?</t>
+  </si>
+  <si>
+    <t>RCA will require user to describe workflow for new user who has never used the product.</t>
+  </si>
+  <si>
+    <t>RCA will require user to manually enter the business purpose of the product.</t>
+  </si>
+  <si>
+    <t>Cross compare this section for impact on ambiguities, open questions and assumptions.</t>
+  </si>
+  <si>
+    <t>Describe the types of users</t>
+  </si>
+  <si>
+    <t>This requirement capture app (RCA) will only state that lets proceed with describing the types of users.</t>
+  </si>
+  <si>
+    <t>D1.2.3.1</t>
+  </si>
+  <si>
+    <t>Will you have a normal user who only looks at reading data from your product?</t>
+  </si>
+  <si>
+    <t>D1.2.3.2</t>
+  </si>
+  <si>
+    <t>Will you have a normal user who only looks at writing data to your product?</t>
+  </si>
+  <si>
+    <t>D1.2.3.3</t>
+  </si>
+  <si>
+    <t>Will you have a paid/premium user who looks at writing data to your product and seeking paid/premium features to access?</t>
+  </si>
+  <si>
+    <t>Write normal user check</t>
+  </si>
+  <si>
+    <t>Read-only normal user check</t>
+  </si>
+  <si>
+    <t>Write paid/premium user check</t>
+  </si>
+  <si>
+    <t>D1.2.3.4</t>
+  </si>
+  <si>
+    <t>Will the paid user segment be divided as well with some a paid-lite users and other premium-heavy users? Or do we have more categories?</t>
+  </si>
+  <si>
+    <t>D1.2.3.5</t>
+  </si>
+  <si>
+    <t>Do you need an admin page for colleagues working on your product?</t>
+  </si>
+  <si>
+    <t>Do you need a super-admin page for your product?</t>
+  </si>
+  <si>
+    <t>Check if product needs admin login.</t>
+  </si>
+  <si>
+    <t>Check if product needs super-admin login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you need files to be stored on Github or only locally? A github repo with same name as in </t>
+  </si>
+  <si>
+    <t>Check if Github is needed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lets proceed with a list of functions for your product. </t>
+  </si>
+  <si>
+    <t>To split the product in specific functions.</t>
+  </si>
+  <si>
+    <t>D1.4.1</t>
+  </si>
+  <si>
+    <t>To get the list of functions that comprise the product.</t>
+  </si>
+  <si>
+    <t>D1.4.2.1</t>
+  </si>
+  <si>
+    <t>Name of function 1</t>
+  </si>
+  <si>
+    <t>Get a list of names of all the functions</t>
+  </si>
+  <si>
+    <t>D1.4.2.x</t>
+  </si>
+  <si>
+    <t>Name of function x</t>
+  </si>
+  <si>
+    <t>Check if the names are proper and make sense and are not random.</t>
+  </si>
+  <si>
+    <t>Lets summarize each function noted</t>
+  </si>
+  <si>
+    <t>This requirement capture app (RCA) will only state that lets proceed with describing the functions.</t>
+  </si>
+  <si>
+    <t>Function 1 summary</t>
+  </si>
+  <si>
+    <t>Function x summary</t>
+  </si>
+  <si>
+    <t>Summary of function 1</t>
+  </si>
+  <si>
+    <t>Summary of function x</t>
+  </si>
+  <si>
+    <t>How many functions? Enter Integer. Imagine we are cutting the product horizontally. How many different slices can be made?</t>
+  </si>
+  <si>
+    <t>D1.2.3.6</t>
+  </si>
+  <si>
+    <t>How many different sub-types of paid/premium users will you need?</t>
+  </si>
+  <si>
+    <t>D1.6</t>
+  </si>
+  <si>
+    <t>To split the product in specific infrastructure</t>
+  </si>
+  <si>
+    <t>What type of infrastructure will your product need? Split the infrastructure as per use cases.</t>
+  </si>
+  <si>
+    <t>Webapp for normal read-only and paid/premium users?</t>
+  </si>
+  <si>
+    <t>Webapp for admin users and super-admins?</t>
+  </si>
+  <si>
+    <t>If public facing webapp is required?</t>
+  </si>
+  <si>
+    <t>If private webapp is required?</t>
+  </si>
+  <si>
+    <t>Android app for normal and paid/premium users?</t>
+  </si>
+  <si>
+    <t>If public facing android app is required?</t>
+  </si>
+  <si>
+    <t>D1.6.4</t>
+  </si>
+  <si>
+    <t>If private android app is required?</t>
+  </si>
+  <si>
+    <t>D1.6.5</t>
+  </si>
+  <si>
+    <t>BFF with public URL for normal and paid/premium users?</t>
+  </si>
+  <si>
+    <t>If public facing URL with BFF is required?</t>
+  </si>
+  <si>
+    <t>BFF with private URL?</t>
+  </si>
+  <si>
+    <t>Permanent Database backend ?</t>
+  </si>
+  <si>
+    <t>Permanent Database functions?</t>
+  </si>
+  <si>
+    <t>In-store memory database functions?</t>
+  </si>
+  <si>
+    <t>In-store memory database?</t>
+  </si>
+  <si>
+    <t>If private URL is required? For login, external endpoints and admins/super-admins, private URLs can be required.</t>
+  </si>
+  <si>
+    <t>D1.6.1.1</t>
+  </si>
+  <si>
+    <t>D1.6.1.2</t>
+  </si>
+  <si>
+    <t>D1.6.1.3</t>
+  </si>
+  <si>
+    <t>Where will it be hosted?</t>
+  </si>
+  <si>
+    <t>What language is expected to be used?</t>
+  </si>
+  <si>
+    <t>CF Pages</t>
+  </si>
+  <si>
+    <t>Hono TS</t>
+  </si>
+  <si>
+    <t>D1.6.2.1</t>
+  </si>
+  <si>
+    <t>D1.6.2.2</t>
+  </si>
+  <si>
+    <t>D1.6.2.3</t>
+  </si>
+  <si>
+    <t>Will the external products interface with the product? E.g.  External SMS reciever or External SMS sender or Payment gateway like Razorpay.</t>
+  </si>
+  <si>
+    <t>D1.6.3.1</t>
+  </si>
+  <si>
+    <t>D1.6.3.2</t>
+  </si>
+  <si>
+    <t>D1.6.3.3</t>
+  </si>
+  <si>
+    <t>Where will it be built? Local/ Github actions?</t>
+  </si>
+  <si>
+    <t>To check if github.yml is required.</t>
+  </si>
+  <si>
+    <t>Kotlin/KMM</t>
+  </si>
+  <si>
+    <t>D1.6.4.2</t>
+  </si>
+  <si>
+    <t>D1.6.4.3</t>
+  </si>
+  <si>
+    <t>Required?</t>
+  </si>
+  <si>
+    <t>Supabase Cloud Edge Functions</t>
+  </si>
+  <si>
+    <t>CF Worker</t>
+  </si>
+  <si>
+    <t>D1.6.6.2</t>
+  </si>
+  <si>
+    <t>D1.6.6.1</t>
+  </si>
+  <si>
+    <t>D1.6.6.3</t>
+  </si>
+  <si>
+    <t>D1.6.7.1</t>
+  </si>
+  <si>
+    <t>D1.6.7.2</t>
+  </si>
+  <si>
+    <t>D1.6.7.3</t>
+  </si>
+  <si>
+    <t>D1.6.8.1</t>
+  </si>
+  <si>
+    <t>D1.6.8.2</t>
+  </si>
+  <si>
+    <t>D1.6.8.3</t>
+  </si>
+  <si>
+    <t>D1.6.9.1</t>
+  </si>
+  <si>
+    <t>D1.6.9.2</t>
+  </si>
+  <si>
+    <t>D1.6.9.3</t>
+  </si>
+  <si>
+    <t>D1.6.10.1</t>
+  </si>
+  <si>
+    <t>D1.6.10.2</t>
+  </si>
+  <si>
+    <t>D1.6.10.3</t>
+  </si>
+  <si>
+    <t>Hetzner Coolify</t>
+  </si>
+  <si>
+    <t>What database?</t>
+  </si>
+  <si>
+    <t>Dragonfly/ Redis</t>
+  </si>
+  <si>
+    <t>Python/Cpp/Rust/Go</t>
+  </si>
+  <si>
+    <t>Supabase Cloud</t>
+  </si>
+  <si>
+    <t>Postgres</t>
+  </si>
+  <si>
+    <t>To check if external products will interface?</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D3.1</t>
+  </si>
+  <si>
+    <t>D3.2</t>
+  </si>
+  <si>
+    <t>Will it interface with BFF or Permanent Database Backend function or In-memory database backend function? Check the boxes.</t>
+  </si>
+  <si>
+    <t>D3.3.1</t>
+  </si>
+  <si>
+    <t>D3.3.j</t>
+  </si>
+  <si>
+    <t>Which  external function intefaces with BFF?</t>
+  </si>
+  <si>
+    <t>Jth external function that interfaces with BFF</t>
+  </si>
+  <si>
+    <t>Initial external function that interfaces with BFF</t>
+  </si>
+  <si>
+    <t>Which  external product intefaces with BFF? Keep on asking, is there another external product that interfaces with BFF?</t>
+  </si>
+  <si>
+    <t>Which  external product intefaces with permanent database backend?</t>
+  </si>
+  <si>
+    <t>Initial external function that interfaces with permanent database backend specifically functions</t>
+  </si>
+  <si>
+    <t>Kth external function that interfaces with permanent database backend specifically functions</t>
+  </si>
+  <si>
+    <t>To check how the external products interface.</t>
+  </si>
+  <si>
+    <t>D3.4.1</t>
+  </si>
+  <si>
+    <t>D3.4.k</t>
+  </si>
+  <si>
+    <t>D3.5.1</t>
+  </si>
+  <si>
+    <t>Which  external product intefaces with in-memory database backend?</t>
+  </si>
+  <si>
+    <t>D3.5.i</t>
+  </si>
+  <si>
+    <t>Ith external function that interfaces with in-memory database backend specifically functions</t>
+  </si>
+  <si>
+    <t>Initial external function that interfaces with in-memory database backend specifically functions</t>
+  </si>
+  <si>
+    <t>Generic description of each function and scope of each function wrt to infrastructure like webapp, android app, BFF and Backend.</t>
+  </si>
+  <si>
+    <t>D2.1.1</t>
+  </si>
+  <si>
+    <t>D2.1.x</t>
+  </si>
+  <si>
+    <t>Lets start with External linkages for externla products</t>
+  </si>
+  <si>
+    <t>This requirement capture app (RCA) will only state that lets proceed with capturing details of the external linkages</t>
+  </si>
+  <si>
+    <t>D2.2.1</t>
+  </si>
+  <si>
+    <t>Does it impact public webapp, private webapp, public BFF, private BFF, permanent database, in-memory database, any external links?</t>
+  </si>
+  <si>
+    <t>For function 1, lets scope its impact? Show tickboxes for all public webapp, private webapp, public BFF, private BFF, permanent database, in-memory database, any external links</t>
+  </si>
+  <si>
+    <t>D2.2.x</t>
+  </si>
+  <si>
+    <t>For function x, lets scope its impact? Show tickboxes for all public webapp, private webapp, public BFF, private BFF, permanent database, in-memory database, any external links</t>
+  </si>
+  <si>
+    <t>Keep on  scope checkbox questions for all functions from 1-x  as above.</t>
+  </si>
+  <si>
+    <t>Autogeneated checks start</t>
+  </si>
+  <si>
+    <t>Check start</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>Self-check of function 1. Description and scope not clear. Something missing in description or ambiguious?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check function 1 vs function 2. Are they overlapping? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check function 1 vs function 3. Are they overlapping? </t>
+  </si>
+  <si>
+    <t>D5.1.1</t>
+  </si>
+  <si>
+    <t>D5.1.2</t>
+  </si>
+  <si>
+    <t>D5.1.3</t>
+  </si>
+  <si>
+    <t>D5.1.x</t>
+  </si>
+  <si>
+    <t>Check function 1 vs function x. Any overlap between descriotion?</t>
+  </si>
+  <si>
+    <t>D5.2.1</t>
+  </si>
+  <si>
+    <t>Check finction 2 vs function 1. Any overlap or ambiguity or assumption or open</t>
+  </si>
+  <si>
+    <t>D5.2.2</t>
+  </si>
+  <si>
+    <t>Self-check of finction 2</t>
+  </si>
+  <si>
+    <t>D5.x.1</t>
+  </si>
+  <si>
+    <t>D5.x.x</t>
+  </si>
+  <si>
+    <t>Self-check of function x.</t>
+  </si>
+  <si>
+    <t>Check function x versus 1. Any overlap between description or any ambiguity?</t>
+  </si>
+  <si>
+    <t>Checks for assumptions, ambiguities and open questions.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +845,20 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -350,7 +917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -368,6 +935,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -748,23 +1324,23 @@
         <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -772,35 +1348,35 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -808,35 +1384,35 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -844,31 +1420,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -876,31 +1452,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3">
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -908,31 +1484,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3">
         <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -940,31 +1516,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3">
         <v>6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -972,31 +1548,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C9" s="3">
         <v>7</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="H9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -1004,34 +1580,1790 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3">
         <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581B6C60-5ACF-4FEC-90F4-0E94D7E97E86}">
+  <dimension ref="A1:M72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="2"/>
+    <col min="3" max="3" width="14.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="42.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.5703125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H61" s="3"/>
+    </row>
+    <row r="62" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H62" s="3"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documents/Refined_proposal_ChatGPT.xlsx
+++ b/Documents/Refined_proposal_ChatGPT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Business\Agentic Code\Requirements_Tool_Local_AI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4160EB37-4130-4891-A192-A475C420ED4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8703169E-296A-40FC-8C89-A0932C32DF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D17E0A88-1C2D-4A27-9B15-EB45CA17BC10}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="296">
   <si>
     <t>Stage</t>
   </si>
@@ -358,9 +358,6 @@
     <t>RCA will require user to manually enter the business purpose of the product.</t>
   </si>
   <si>
-    <t>Cross compare this section for impact on ambiguities, open questions and assumptions.</t>
-  </si>
-  <si>
     <t>Describe the types of users</t>
   </si>
   <si>
@@ -415,9 +412,6 @@
     <t>Check if product needs super-admin login</t>
   </si>
   <si>
-    <t xml:space="preserve">Do you need files to be stored on Github or only locally? A github repo with same name as in </t>
-  </si>
-  <si>
     <t>Check if Github is needed?</t>
   </si>
   <si>
@@ -754,9 +748,6 @@
     <t>D2.2.1</t>
   </si>
   <si>
-    <t>Does it impact public webapp, private webapp, public BFF, private BFF, permanent database, in-memory database, any external links?</t>
-  </si>
-  <si>
     <t>For function 1, lets scope its impact? Show tickboxes for all public webapp, private webapp, public BFF, private BFF, permanent database, in-memory database, any external links</t>
   </si>
   <si>
@@ -769,9 +760,6 @@
     <t>Keep on  scope checkbox questions for all functions from 1-x  as above.</t>
   </si>
   <si>
-    <t>Autogeneated checks start</t>
-  </si>
-  <si>
     <t>Check start</t>
   </si>
   <si>
@@ -799,21 +787,12 @@
     <t>D5.1.x</t>
   </si>
   <si>
-    <t>Check function 1 vs function x. Any overlap between descriotion?</t>
-  </si>
-  <si>
     <t>D5.2.1</t>
   </si>
   <si>
-    <t>Check finction 2 vs function 1. Any overlap or ambiguity or assumption or open</t>
-  </si>
-  <si>
     <t>D5.2.2</t>
   </si>
   <si>
-    <t>Self-check of finction 2</t>
-  </si>
-  <si>
     <t>D5.x.1</t>
   </si>
   <si>
@@ -827,13 +806,124 @@
   </si>
   <si>
     <t>Checks for assumptions, ambiguities and open questions.</t>
+  </si>
+  <si>
+    <t>Tag (Stage_Output_Deliverables_ManualorAI_entering_time)</t>
+  </si>
+  <si>
+    <t>Manually_Accepted_AI_Proposal</t>
+  </si>
+  <si>
+    <t>Tag Legend for AorM</t>
+  </si>
+  <si>
+    <t>Manually_Rejected_AI_Proposal</t>
+  </si>
+  <si>
+    <t>Does it impact public webapp, private webapp, public BFF, private BFF, permanent database, in-memory database, any external links? (Enumerate all the infrastructure as captured in section 1.6  and section 3)</t>
+  </si>
+  <si>
+    <t>Manually_Edited_AI_Proposal</t>
+  </si>
+  <si>
+    <t>MEAP</t>
+  </si>
+  <si>
+    <t>MAAP</t>
+  </si>
+  <si>
+    <t>MRAP</t>
+  </si>
+  <si>
+    <t>Check function 1 vs function x. Any overlap between description?</t>
+  </si>
+  <si>
+    <t>Self-check of function 2</t>
+  </si>
+  <si>
+    <t>Check function 2 vs function 1. Any overlap or ambiguity or assumption or open</t>
+  </si>
+  <si>
+    <t>Self-check for functions is from D5.1.1-&gt;D5.x.x. Self-check involves following: 
+1) Check summary and work out expected impact on all infrastructure like  public webapp, private webapp, public BFF, private BFF, permanent database, in-memory database, any external links using LLM. Compare to manually entered values in D2.2.x. Is this same, if expected not same as entered, raise ambiguity, assumption or open question.
+2) Compare the product description( section 1.2) vs D5.x.x to work out if any user impact is missing? any users not recorded or missing?</t>
+  </si>
+  <si>
+    <t>1) Check function 1 summary vs function 2 summary. Are they similar or different? If similar, raise ambiguity. 
+2) Can they be combined into one function although dissimilar by design? Raise open question after LLM analysis. If better to be 2 different functions, then dont raise open question.</t>
+  </si>
+  <si>
+    <t>Autogenerated checks start</t>
+  </si>
+  <si>
+    <t>Questions and Statements made from Column Deliverables.</t>
+  </si>
+  <si>
+    <t>Hint for Answers is given in column "Reason for Requesting"</t>
+  </si>
+  <si>
+    <t>Based on Column "Manually typed in Initially", some answers are typed in manually from the questions.</t>
+  </si>
+  <si>
+    <t>Answers are subject to different types of LLM reviews.</t>
+  </si>
+  <si>
+    <t>Statement only. Cross compare this section for impact on ambiguities, open questions and assumptions.</t>
+  </si>
+  <si>
+    <t>Do you need files to be stored on Github or only locally? A github repo with same name as in D1.1 will be started.</t>
+  </si>
+  <si>
+    <t>Setting up Github folder only</t>
+  </si>
+  <si>
+    <t>Stage LLM review will be carried out in sequence after all manual fields filled in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM Review will highlight ambiguities, open questions and assumptions for every task marked as needing "LLM Review" in column. </t>
+  </si>
+  <si>
+    <t>Manually_Generated_firstpass</t>
+  </si>
+  <si>
+    <t>AI_Generated_firstpass</t>
+  </si>
+  <si>
+    <t>MGFP</t>
+  </si>
+  <si>
+    <t>AGFP</t>
+  </si>
+  <si>
+    <t>AI_Generated_Review_Manualentry</t>
+  </si>
+  <si>
+    <t>AGRM</t>
+  </si>
+  <si>
+    <t>If reference to section number is made in "Reason for LLM Review" e.g. D5, then skip review for that tag. The review will be conducted in section noted.</t>
+  </si>
+  <si>
+    <t>This LLM Review will be done one by one for each in "Tag" column by LLM selected (Either local LLM via Ollama or Cloud LLM via key)</t>
+  </si>
+  <si>
+    <t>Tool Requirements</t>
+  </si>
+  <si>
+    <t>Tag Requirements</t>
+  </si>
+  <si>
+    <t>Select tag MGFP if this is first time manually generated.</t>
+  </si>
+  <si>
+    <t>LLM review will be marked AGRM as per tag legend when it has been created. If reviewed but no comments, it should still be marked AGRM since review was done. Tags to be done as per "Tag" colum. If review skipped, then don’t tag at all.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,8 +953,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -886,6 +984,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -917,7 +1027,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -940,10 +1050,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1327,7 +1446,7 @@
         <v>80</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>15</v>
@@ -1614,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581B6C60-5ACF-4FEC-90F4-0E94D7E97E86}">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:S71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="2"/>
@@ -1624,10 +1743,18 @@
     <col min="6" max="6" width="24.140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="26.5703125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="9" max="9" width="35.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="2"/>
+    <col min="12" max="12" width="22.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" style="2" customWidth="1"/>
+    <col min="14" max="17" width="9.140625" style="2"/>
+    <col min="18" max="18" width="20.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1652,13 +1779,23 @@
       <c r="H1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="I1" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="9" t="s">
+        <v>262</v>
+      </c>
       <c r="M1" s="9"/>
-    </row>
-    <row r="2" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="R1" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>82</v>
       </c>
@@ -1683,8 +1820,22 @@
       <c r="H2" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="I2" s="3" t="str">
+        <f>A2&amp;"_"&amp;B2&amp;"_"&amp;C2&amp;"_(AorM)_(time)"</f>
+        <v>S1_PRD_D1.1_(AorM)_(time)</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="S2" s="11"/>
+    </row>
+    <row r="3" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>82</v>
       </c>
@@ -1707,10 +1858,24 @@
         <v>98</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="I3" s="3" t="str">
+        <f t="shared" ref="I3:I66" si="0">A3&amp;"_"&amp;B3&amp;"_"&amp;C3&amp;"_(AorM)_(time)"</f>
+        <v>S1_PRD_D1.2_(AorM)_(time)</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="S3" s="11"/>
+    </row>
+    <row r="4" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -1733,10 +1898,26 @@
         <v>92</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="I4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.1_(AorM)_(time)</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>82</v>
       </c>
@@ -1758,9 +1939,25 @@
       <c r="G5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="H5" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I5" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.2_(AorM)_(time)</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="S5" s="11"/>
+    </row>
+    <row r="6" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>82</v>
       </c>
@@ -1771,10 +1968,10 @@
         <v>102</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>98</v>
@@ -1785,8 +1982,22 @@
       <c r="H6" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="I6" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.3_(AorM)_(time)</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="S6" s="11"/>
+    </row>
+    <row r="7" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>82</v>
       </c>
@@ -1794,143 +2005,199 @@
         <v>84</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.3.1_(AorM)_(time)</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="R7" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="S7" s="11"/>
+    </row>
+    <row r="8" spans="1:19" ht="195" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I8" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.3.2_(AorM)_(time)</v>
+      </c>
+      <c r="R8" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="S8" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I9" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.3.3_(AorM)_(time)</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="S9" s="11"/>
+    </row>
+    <row r="10" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I10" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.3.4_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I11" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.3.5_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="H12" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I12" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.2.3.6_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>82</v>
       </c>
@@ -1941,20 +2208,26 @@
         <v>87</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="I13" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>82</v>
       </c>
@@ -1965,10 +2238,10 @@
         <v>88</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>98</v>
@@ -1979,8 +2252,12 @@
       <c r="H14" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="I14" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.4_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>82</v>
       </c>
@@ -1988,87 +2265,103 @@
         <v>84</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.4.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.4.2.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.4.2.x_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>98</v>
@@ -2079,8 +2372,12 @@
       <c r="H18" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>82</v>
       </c>
@@ -2088,23 +2385,29 @@
         <v>84</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="F19" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H19" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D2.1.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -2112,23 +2415,29 @@
         <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="H20" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D2.1.x_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -2136,13 +2445,13 @@
         <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>98</v>
@@ -2153,8 +2462,12 @@
       <c r="H21" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="I21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
@@ -2162,733 +2475,913 @@
         <v>84</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.1.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.1.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.1.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.2.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.2.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.2.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.3.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I29" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.3.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I30" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.3.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I31" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.4_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I32" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.4.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I33" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.4.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I34" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.5_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="E35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I35" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.2.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="F36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I36" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.2.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I37" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.6.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I38" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.6.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="F39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I39" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.6.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I40" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.7.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I41" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.7.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I42" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.7.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I43" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.8.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I44" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.8.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="F45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I45" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.8.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="F46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I46" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.9.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I47" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.9.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I48" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.9.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D42" s="3" t="s">
+      <c r="E49" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I49" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.10.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I50" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.10.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="F51" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="H51" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I51" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D1.6.10.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>215</v>
+      <c r="C52" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>98</v>
@@ -2899,8 +3392,12 @@
       <c r="H52" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="I52" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>82</v>
       </c>
@@ -2908,191 +3405,239 @@
         <v>84</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I53" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I54" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D55" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I55" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.3.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="D56" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I56" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.3.j_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I57" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.4.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" s="3" t="s">
+      <c r="E58" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I58" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.4.k_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="E59" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I59" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.5.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D60" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="F60" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="H60" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I60" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D3.5.i_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>82</v>
       </c>
@@ -3100,61 +3645,73 @@
         <v>84</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D2.2.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D62" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C62" s="3" t="s">
+      <c r="F62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I62" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D2.2.x_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>98</v>
@@ -3165,8 +3722,12 @@
       <c r="H63" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="I63" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D5_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="210" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>82</v>
       </c>
@@ -3174,12 +3735,14 @@
         <v>84</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E64" s="3"/>
+        <v>246</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="F64" s="3" t="s">
         <v>98</v>
       </c>
@@ -3187,10 +3750,14 @@
         <v>92</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="I64" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D5.1.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>82</v>
       </c>
@@ -3198,12 +3765,14 @@
         <v>84</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E65" s="3"/>
+        <v>247</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="F65" s="3" t="s">
         <v>98</v>
       </c>
@@ -3211,10 +3780,14 @@
         <v>92</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="I65" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D5.1.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>82</v>
       </c>
@@ -3222,10 +3795,10 @@
         <v>84</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
@@ -3235,10 +3808,14 @@
         <v>92</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="I66" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>S1_PRD_D5.1.3_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>82</v>
       </c>
@@ -3246,10 +3823,10 @@
         <v>84</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
@@ -3259,10 +3836,14 @@
         <v>92</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="I67" s="3" t="str">
+        <f t="shared" ref="I67:I71" si="1">A67&amp;"_"&amp;B67&amp;"_"&amp;C67&amp;"_(AorM)_(time)"</f>
+        <v>S1_PRD_D5.1.x_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>82</v>
       </c>
@@ -3270,10 +3851,10 @@
         <v>84</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
@@ -3283,10 +3864,14 @@
         <v>92</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="I68" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>S1_PRD_D5.2.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>82</v>
       </c>
@@ -3294,10 +3879,10 @@
         <v>84</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
@@ -3307,10 +3892,14 @@
         <v>92</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="I69" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>S1_PRD_D5.2.2_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>82</v>
       </c>
@@ -3318,10 +3907,10 @@
         <v>84</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
@@ -3331,10 +3920,14 @@
         <v>92</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="I70" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>S1_PRD_D5.x.1_(AorM)_(time)</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>82</v>
       </c>
@@ -3342,25 +3935,25 @@
         <v>84</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="I71" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>S1_PRD_D5.x.x_(AorM)_(time)</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Documents/Refined_proposal_ChatGPT.xlsx
+++ b/Documents/Refined_proposal_ChatGPT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Business\Agentic Code\Requirements_Tool_Local_AI\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8703169E-296A-40FC-8C89-A0932C32DF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E67A901-EC41-46BF-90E0-5F750B213A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D17E0A88-1C2D-4A27-9B15-EB45CA17BC10}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="306">
   <si>
     <t>Stage</t>
   </si>
@@ -499,13 +499,7 @@
     <t>If public facing android app is required?</t>
   </si>
   <si>
-    <t>D1.6.4</t>
-  </si>
-  <si>
     <t>If private android app is required?</t>
-  </si>
-  <si>
-    <t>D1.6.5</t>
   </si>
   <si>
     <t>BFF with public URL for normal and paid/premium users?</t>
@@ -917,6 +911,42 @@
   </si>
   <si>
     <t>LLM review will be marked AGRM as per tag legend when it has been created. If reviewed but no comments, it should still be marked AGRM since review was done. Tags to be done as per "Tag" colum. If review skipped, then don’t tag at all.</t>
+  </si>
+  <si>
+    <t>The entire history of Manual additions and AI reviews will be captured via tags in a json file. This will allow all choices to be replayed. Note that the "Tag" column includes a time field. So when manually entered, time of entry will be added here. If AI review is done, the time of AI review completion willl be here. If AI review accepted manually, that time of acceptance will be in this field. Same for edited or rejected.</t>
+  </si>
+  <si>
+    <t>D1.6.5.2</t>
+  </si>
+  <si>
+    <t>D1.6.5.3</t>
+  </si>
+  <si>
+    <t>D1.6.5.1</t>
+  </si>
+  <si>
+    <t>D1.6.4.1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>LLM to be requested to generate a context diagram of entire product based on all the above content reviewed.</t>
+  </si>
+  <si>
+    <t>Context Diagram of Product</t>
+  </si>
+  <si>
+    <t>Max_functions_per_product = 10</t>
+  </si>
+  <si>
+    <t>The json file shall be automatically saved when clicking D5 autochecks.</t>
+  </si>
+  <si>
+    <t>There shall be a button to periodically save the json file.</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1476,7 @@
         <v>80</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>15</v>
@@ -1733,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581B6C60-5ACF-4FEC-90F4-0E94D7E97E86}">
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="2"/>
@@ -1749,7 +1779,7 @@
     <col min="12" max="12" width="22.28515625" style="2" customWidth="1"/>
     <col min="13" max="13" width="12.140625" style="2" customWidth="1"/>
     <col min="14" max="17" width="9.140625" style="2"/>
-    <col min="18" max="18" width="20.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="22.7109375" style="2" customWidth="1"/>
     <col min="19" max="19" width="19.5703125" style="2" customWidth="1"/>
     <col min="20" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -1780,19 +1810,19 @@
         <v>94</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
       <c r="L1" s="9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M1" s="9"/>
       <c r="R1" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -1825,13 +1855,13 @@
         <v>S1_PRD_D1.1_(AorM)_(time)</v>
       </c>
       <c r="L2" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="M2" s="10" t="s">
-        <v>286</v>
-      </c>
       <c r="R2" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="S2" s="11"/>
     </row>
@@ -1858,20 +1888,20 @@
         <v>98</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I3" s="3" t="str">
         <f t="shared" ref="I3:I66" si="0">A3&amp;"_"&amp;B3&amp;"_"&amp;C3&amp;"_(AorM)_(time)"</f>
         <v>S1_PRD_D1.2_(AorM)_(time)</v>
       </c>
       <c r="L3" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="M3" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="M3" s="10" t="s">
-        <v>287</v>
-      </c>
       <c r="R3" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="S3" s="11"/>
     </row>
@@ -1898,23 +1928,23 @@
         <v>92</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.1_(AorM)_(time)</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -1940,20 +1970,20 @@
         <v>92</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.2_(AorM)_(time)</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="S5" s="11"/>
     </row>
@@ -1987,13 +2017,13 @@
         <v>S1_PRD_D1.2.3_(AorM)_(time)</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="R6" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S6" s="11"/>
     </row>
@@ -2020,20 +2050,20 @@
         <v>92</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.3.1_(AorM)_(time)</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="S7" s="11"/>
     </row>
@@ -2060,17 +2090,17 @@
         <v>92</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.3.2_(AorM)_(time)</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -2096,18 +2126,18 @@
         <v>92</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.3.3_(AorM)_(time)</v>
       </c>
       <c r="R9" s="11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="S9" s="11"/>
     </row>
-    <row r="10" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="285" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>82</v>
       </c>
@@ -2130,11 +2160,14 @@
         <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.3.4_(AorM)_(time)</v>
+      </c>
+      <c r="R10" s="11" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -2160,14 +2193,17 @@
         <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.3.5_(AorM)_(time)</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="R11" s="11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>82</v>
       </c>
@@ -2190,11 +2226,14 @@
         <v>92</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.2.3.6_(AorM)_(time)</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -2208,7 +2247,7 @@
         <v>87</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>128</v>
@@ -2220,11 +2259,14 @@
         <v>98</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>S1_PRD_D1.3_(AorM)_(time)</v>
+      </c>
+      <c r="R13" s="11" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -2280,7 +2322,7 @@
         <v>92</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2340,7 +2382,7 @@
         <v>92</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2355,7 +2397,7 @@
         <v>84</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>139</v>
@@ -2385,7 +2427,7 @@
         <v>84</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>141</v>
@@ -2400,7 +2442,7 @@
         <v>92</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I19" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2415,7 +2457,7 @@
         <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>142</v>
@@ -2430,7 +2472,7 @@
         <v>92</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I20" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2475,7 +2517,7 @@
         <v>84</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>151</v>
@@ -2490,7 +2532,7 @@
         <v>92</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I22" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2505,14 +2547,14 @@
         <v>84</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="F23" s="3" t="s">
         <v>92</v>
       </c>
@@ -2520,7 +2562,7 @@
         <v>92</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I23" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2535,14 +2577,14 @@
         <v>84</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>92</v>
       </c>
@@ -2550,7 +2592,7 @@
         <v>92</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2565,7 +2607,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>152</v>
@@ -2580,7 +2622,7 @@
         <v>92</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2595,14 +2637,14 @@
         <v>84</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="F26" s="3" t="s">
         <v>92</v>
       </c>
@@ -2610,7 +2652,7 @@
         <v>92</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2625,14 +2667,14 @@
         <v>84</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="F27" s="3" t="s">
         <v>92</v>
       </c>
@@ -2640,7 +2682,7 @@
         <v>92</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2655,7 +2697,7 @@
         <v>84</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>155</v>
@@ -2670,7 +2712,7 @@
         <v>92</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2685,13 +2727,13 @@
         <v>84</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>92</v>
@@ -2700,7 +2742,7 @@
         <v>92</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2715,13 +2757,13 @@
         <v>84</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>92</v>
@@ -2730,7 +2772,7 @@
         <v>92</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2745,13 +2787,13 @@
         <v>84</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>157</v>
+        <v>298</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>155</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>92</v>
@@ -2760,11 +2802,11 @@
         <v>92</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I31" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>S1_PRD_D1.6.4_(AorM)_(time)</v>
+        <v>S1_PRD_D1.6.4.1_(AorM)_(time)</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2775,13 +2817,13 @@
         <v>84</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>92</v>
@@ -2790,7 +2832,7 @@
         <v>92</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I32" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2805,13 +2847,13 @@
         <v>84</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>92</v>
@@ -2820,7 +2862,7 @@
         <v>92</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I33" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2835,14 +2877,14 @@
         <v>84</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="F34" s="3" t="s">
         <v>92</v>
       </c>
@@ -2850,11 +2892,11 @@
         <v>92</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I34" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>S1_PRD_D1.6.5_(AorM)_(time)</v>
+        <v>S1_PRD_D1.6.5.1_(AorM)_(time)</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2865,13 +2907,13 @@
         <v>84</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>176</v>
+        <v>295</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>92</v>
@@ -2880,11 +2922,11 @@
         <v>92</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I35" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>S1_PRD_D1.6.2.2_(AorM)_(time)</v>
+        <v>S1_PRD_D1.6.5.2_(AorM)_(time)</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2895,14 +2937,14 @@
         <v>84</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>177</v>
+        <v>296</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="F36" s="3" t="s">
         <v>92</v>
       </c>
@@ -2910,11 +2952,11 @@
         <v>92</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I36" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>S1_PRD_D1.6.2.3_(AorM)_(time)</v>
+        <v>S1_PRD_D1.6.5.3_(AorM)_(time)</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -2925,13 +2967,13 @@
         <v>84</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>92</v>
@@ -2940,7 +2982,7 @@
         <v>92</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2955,13 +2997,13 @@
         <v>84</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>92</v>
@@ -2970,7 +3012,7 @@
         <v>92</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I38" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2985,14 +3027,14 @@
         <v>84</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="F39" s="3" t="s">
         <v>92</v>
       </c>
@@ -3000,7 +3042,7 @@
         <v>92</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3015,13 +3057,13 @@
         <v>84</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>92</v>
@@ -3030,7 +3072,7 @@
         <v>92</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I40" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3045,13 +3087,13 @@
         <v>84</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>92</v>
@@ -3060,7 +3102,7 @@
         <v>92</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3075,13 +3117,13 @@
         <v>84</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>92</v>
@@ -3090,7 +3132,7 @@
         <v>92</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3105,13 +3147,13 @@
         <v>84</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>92</v>
@@ -3120,7 +3162,7 @@
         <v>92</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I43" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3135,13 +3177,13 @@
         <v>84</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>92</v>
@@ -3150,7 +3192,7 @@
         <v>92</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I44" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3165,14 +3207,14 @@
         <v>84</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>92</v>
       </c>
@@ -3180,7 +3222,7 @@
         <v>92</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I45" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3195,13 +3237,13 @@
         <v>84</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>92</v>
@@ -3210,7 +3252,7 @@
         <v>92</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I46" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3225,13 +3267,13 @@
         <v>84</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>92</v>
@@ -3240,7 +3282,7 @@
         <v>92</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I47" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3255,13 +3297,13 @@
         <v>84</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>92</v>
@@ -3270,7 +3312,7 @@
         <v>92</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I48" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3285,13 +3327,13 @@
         <v>84</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>92</v>
@@ -3300,7 +3342,7 @@
         <v>92</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I49" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3315,14 +3357,14 @@
         <v>84</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="F50" s="3" t="s">
         <v>92</v>
       </c>
@@ -3330,7 +3372,7 @@
         <v>92</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3345,13 +3387,13 @@
         <v>84</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>92</v>
@@ -3360,7 +3402,7 @@
         <v>92</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I51" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3375,13 +3417,13 @@
         <v>84</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>98</v>
@@ -3405,13 +3447,13 @@
         <v>84</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>92</v>
@@ -3420,7 +3462,7 @@
         <v>92</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3435,13 +3477,13 @@
         <v>84</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>92</v>
@@ -3450,7 +3492,7 @@
         <v>92</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3465,14 +3507,14 @@
         <v>84</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="F55" s="3" t="s">
         <v>92</v>
       </c>
@@ -3480,7 +3522,7 @@
         <v>92</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3495,14 +3537,14 @@
         <v>84</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="F56" s="3" t="s">
         <v>92</v>
       </c>
@@ -3510,7 +3552,7 @@
         <v>92</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3525,13 +3567,13 @@
         <v>84</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>92</v>
@@ -3540,7 +3582,7 @@
         <v>92</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3555,14 +3597,14 @@
         <v>84</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>92</v>
       </c>
@@ -3570,7 +3612,7 @@
         <v>92</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I58" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3585,13 +3627,13 @@
         <v>84</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>92</v>
@@ -3600,7 +3642,7 @@
         <v>92</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I59" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3615,14 +3657,14 @@
         <v>84</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="F60" s="3" t="s">
         <v>92</v>
       </c>
@@ -3630,7 +3672,7 @@
         <v>92</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I60" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3645,13 +3687,13 @@
         <v>84</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>92</v>
@@ -3660,7 +3702,7 @@
         <v>92</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I61" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3675,14 +3717,14 @@
         <v>84</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>92</v>
       </c>
@@ -3690,7 +3732,7 @@
         <v>92</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I62" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3705,13 +3747,13 @@
         <v>84</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>98</v>
@@ -3735,13 +3777,13 @@
         <v>84</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>98</v>
@@ -3750,7 +3792,7 @@
         <v>92</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I64" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3765,13 +3807,13 @@
         <v>84</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>98</v>
@@ -3780,7 +3822,7 @@
         <v>92</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I65" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3795,10 +3837,10 @@
         <v>84</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
@@ -3808,7 +3850,7 @@
         <v>92</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I66" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3823,10 +3865,10 @@
         <v>84</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
@@ -3836,7 +3878,7 @@
         <v>92</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I67" s="3" t="str">
         <f t="shared" ref="I67:I71" si="1">A67&amp;"_"&amp;B67&amp;"_"&amp;C67&amp;"_(AorM)_(time)"</f>
@@ -3851,10 +3893,10 @@
         <v>84</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
@@ -3864,7 +3906,7 @@
         <v>92</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I68" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3879,10 +3921,10 @@
         <v>84</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
@@ -3892,7 +3934,7 @@
         <v>92</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I69" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3907,10 +3949,10 @@
         <v>84</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
@@ -3920,7 +3962,7 @@
         <v>92</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I70" s="3" t="str">
         <f t="shared" si="1"/>
@@ -3935,10 +3977,10 @@
         <v>84</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
@@ -3948,12 +3990,37 @@
         <v>92</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I71" s="3" t="str">
         <f t="shared" si="1"/>
         <v>S1_PRD_D5.x.x_(AorM)_(time)</v>
       </c>
+    </row>
+    <row r="72" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
